--- a/项目测试.xlsx
+++ b/项目测试.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Code\SqlTool\SqlTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7268CD4-43FF-4498-95E1-4C2183F80C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F71033A-C2E5-487E-A58A-E1809D8F1476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3924" yWindow="0" windowWidth="18936" windowHeight="12948" xr2:uid="{350B7CB5-93C6-41E9-AB7D-EB9BE52BD3FE}"/>
+    <workbookView xWindow="3072" yWindow="12" windowWidth="18936" windowHeight="12948" xr2:uid="{350B7CB5-93C6-41E9-AB7D-EB9BE52BD3FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>a</t>
   </si>
   <si>
-    <t>e//</t>
-  </si>
-  <si>
     <t>da</t>
   </si>
   <si>
@@ -163,6 +160,10 @@
   </si>
   <si>
     <t>12299209-1b56-4971-8822-29563a629759.png</t>
+  </si>
+  <si>
+    <t>E:\aaa\ddd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -215,11 +216,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,6 +541,7 @@
   <cols>
     <col min="1" max="1" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.44140625" customWidth="1"/>
     <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="51.44140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -581,12 +583,12 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>45281.923136574071</v>
       </c>
       <c r="F2">
@@ -596,10 +598,10 @@
         <v>2</v>
       </c>
       <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
         <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -607,15 +609,15 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>45278.335902777777</v>
       </c>
       <c r="F3">
@@ -625,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
         <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -636,15 +638,15 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>45278.377916666665</v>
       </c>
       <c r="F4">
@@ -654,10 +656,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -665,15 +667,15 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>45279.386967592596</v>
       </c>
       <c r="F5">
@@ -683,10 +685,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -694,15 +696,15 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>45279.445555555554</v>
       </c>
       <c r="F6">
@@ -712,10 +714,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -723,15 +725,15 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
         <v>29</v>
       </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>45285.237719907411</v>
       </c>
       <c r="F7">
@@ -741,10 +743,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -752,15 +754,15 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
         <v>32</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>33</v>
       </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>45281.923136574071</v>
       </c>
       <c r="F8">
@@ -770,26 +772,26 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
         <v>35</v>
       </c>
-      <c r="I8" t="s">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>37</v>
       </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>45405.357604166667</v>
       </c>
       <c r="F10">
@@ -799,24 +801,24 @@
         <v>4</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>40</v>
       </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>45406.448993055557</v>
       </c>
       <c r="F11">
@@ -826,24 +828,24 @@
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>43</v>
       </c>
-      <c r="D12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>45416.414606481485</v>
       </c>
       <c r="F12">
@@ -853,10 +855,10 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
